--- a/EXAM_FORM1_RESULTS/EXAM_FORM1_62578.xlsx
+++ b/EXAM_FORM1_RESULTS/EXAM_FORM1_62578.xlsx
@@ -617,7 +617,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:L10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -702,24 +702,23 @@
       <c r="A4" t="n">
         <v>3</v>
       </c>
-      <c r="C4" t="n">
-        <v>1</v>
+      <c r="J4" t="n">
+        <v>3</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>XHz</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
         <v>4</v>
       </c>
-      <c r="D5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I5" t="n">
+      <c r="C5" t="n">
         <v>1</v>
       </c>
     </row>
@@ -727,13 +726,45 @@
       <c r="A6" t="n">
         <v>5</v>
       </c>
-      <c r="C6" t="n">
+      <c r="D6" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
         <v>6</v>
+      </c>
+      <c r="J7" t="n">
+        <v>7</v>
+      </c>
+      <c r="K7" t="n">
+        <v>171</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>KHz</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="C8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/EXAM_FORM1_RESULTS/EXAM_FORM1_62578.xlsx
+++ b/EXAM_FORM1_RESULTS/EXAM_FORM1_62578.xlsx
@@ -548,7 +548,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Jeyyv</t>
+          <t>Ile wlal</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>VRDT</t>
+          <t>VLLE LOLT</t>
         </is>
       </c>
     </row>
